--- a/IaR_GaR_April_2026/Outputs/skewt_best_spec_gdp.xlsx
+++ b/IaR_GaR_April_2026/Outputs/skewt_best_spec_gdp.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="210" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="252" uniqueCount="14">
   <si>
     <t>Dates</t>
   </si>
